--- a/contest_database.xlsx
+++ b/contest_database.xlsx
@@ -489,7 +489,7 @@
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -526,7 +526,7 @@
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="G4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="G5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>

--- a/contest_database.xlsx
+++ b/contest_database.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,12 +466,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5260506311</t>
+          <t>7458808931</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>aRakhmatulloyev</t>
+          <t>aRakhmatullayev</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -479,143 +479,1398 @@
           <t>Aziz</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>+998930808167</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5746393294</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Nizomiddin_6585</t>
-        </is>
-      </c>
+          <t>8000346452</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nizomiddin Davronov</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>998916460320</t>
-        </is>
-      </c>
+          <t>нодира `</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>7645219503</t>
+        </is>
+      </c>
       <c r="G3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
         <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>7458808931</t>
+          <t>8066279829</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>aRakhmatullayev</t>
+          <t>dalimovaa_z</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Aziz</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>+998930590253</t>
-        </is>
-      </c>
+          <t>Зилолахон Далимова</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>5260506311</t>
+          <t>8450025303</t>
         </is>
       </c>
       <c r="G4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" t="b">
+      <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6624906306</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Someone2706</t>
-        </is>
-      </c>
+          <t>1970082045</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>.</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>998973006585</t>
-        </is>
-      </c>
+          <t>Dilrabo</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>7645219503</t>
+        </is>
+      </c>
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1809590631</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Najmiddinovna1999</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Sobirov Naimjon</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>5260506311</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aRakhmatulloyev </t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aziz </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>998930808167</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1556643624</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZamiraBaratova </t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zamira Baratova </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>998883002607</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>8610273040</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">moonbyazie </t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aziza✨ </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>998874820306</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>746583343</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nilufar_hamroyeva </t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nilufar Hamroyeva </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>6098487020</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fesleen_rr </t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">𝓡𝓪𝔂𝓱𝓸𝓷🪽 </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1112095102</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xurshida_1019 </t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Xurshidabonu </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>5064887816</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aazonleed </t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dilnoza Fazliddinova </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>8316372149</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ma'murova </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1878190631</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shamsiyeva Sadoqat </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>8265818332</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rahmatulla </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>8000346452</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>нодира `</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>8066279829</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Зилолахон Далимова </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1970082045</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dalimovaa_z </t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dilrabo </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1809590631</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Najmiddinovna1999 </t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sobirov Naimjon </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="b">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>8774860493</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kadirovbro </t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кадиров Бахтиёр </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>5874426896</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Xalmuratov Ernazar </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="b">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1154770583</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zaripa </t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>6370393762</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZEN </t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="b">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>8128289732</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ш' </t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>7825767585</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>m_asilbekk</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>M.A.A</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="b">
+        <v>1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>5746393294</t>
         </is>
       </c>
-      <c r="G5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Nizomiddin_6585</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Nizomiddin Davronov</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="b">
+        <v>1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>824110054</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>JustPlayFootball</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Abdulaziz</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>8138038509</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>MAA_01_07</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Asilbek</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>7825767585</t>
+        </is>
+      </c>
+      <c r="G29" t="b">
+        <v>1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>7204403633</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Istamov_Daler</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Daler Istamov</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="b">
+        <v>1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>8570828023</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ислам</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>5874426896</t>
+        </is>
+      </c>
+      <c r="G31" t="b">
+        <v>1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>7814548611</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>mnrna_g</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>𝑴𝒂𝒏𝒔𝒖𝒓𝒃𝒆𝒌𝒐𝒗𝒏𝒂🤍</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>8450025303</t>
+        </is>
+      </c>
+      <c r="G32" t="b">
+        <v>1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>8448994079</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>miss_guli09</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>🌸</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>7825767585</t>
+        </is>
+      </c>
+      <c r="G33" t="b">
+        <v>0</v>
+      </c>
+      <c r="H33" t="b">
+        <v>0</v>
+      </c>
+      <c r="I33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1091051441</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Munira Sharipova</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1556643624</t>
+        </is>
+      </c>
+      <c r="G34" t="b">
+        <v>1</v>
+      </c>
+      <c r="H34" t="b">
+        <v>0</v>
+      </c>
+      <c r="I34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>5231040512</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>f_beshimov</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Faxriddin</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="b">
+        <v>1</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>7881044808</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Жаксылык</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>5874426896</t>
+        </is>
+      </c>
+      <c r="G36" t="b">
+        <v>1</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1080362116</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Akobir_toshev</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Akobir</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="b">
+        <v>1</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>7344571372</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>John_Adam8</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>John</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1080362116</t>
+        </is>
+      </c>
+      <c r="G38" t="b">
+        <v>1</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>8664374574</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Leo_Carte4</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Leo Carter</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1080362116</t>
+        </is>
+      </c>
+      <c r="G39" t="b">
+        <v>1</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>1750912031</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Rahmatillo_Teshayev</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Rahmatillo</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>8155195994</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Mysteriousnerd</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Abdulloh</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1750912031</t>
+        </is>
+      </c>
+      <c r="G41" t="b">
+        <v>1</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>5526996962</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>rah1mvvv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>𝑅/𝑁</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1750912031</t>
+        </is>
+      </c>
+      <c r="G42" t="b">
+        <v>0</v>
+      </c>
+      <c r="H42" t="b">
+        <v>0</v>
+      </c>
+      <c r="I42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>8804169445</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1080362116</t>
+        </is>
+      </c>
+      <c r="G43" t="b">
+        <v>1</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>7758897425</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ismail Nusrat</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="b">
+        <v>1</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
     </row>
